--- a/samples/ss_slcg_ingest.xlsx
+++ b/samples/ss_slcg_ingest.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SRLYABR</t>
+          <t>SRLYA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
